--- a/Employee_Reports_wi52/Mohamed Riswan Mohamed Salyh Q0334.xlsx
+++ b/Employee_Reports_wi52/Mohamed Riswan Mohamed Salyh Q0334.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-94</v>
+        <v>-102</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1768,11 +1768,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1832,41 +1832,41 @@
       <c r="K29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>728</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
